--- a/longtailpoint/batch_twl-interpolation_586ft.xlsx
+++ b/longtailpoint/batch_twl-interpolation_586ft.xlsx
@@ -6299,7 +6299,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>examples/great_lakes/longtailpoint/batch_twl_output/586ft</t>
+          <t>longtailpoint/batch_twl_output/586ft</t>
         </is>
       </c>
     </row>
